--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.4967477444259</v>
+        <v>5.605721508469208</v>
       </c>
       <c r="D2" t="n">
-        <v>34.57488293700342</v>
+        <v>5.618418477263057</v>
       </c>
       <c r="E2" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F2" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.81350109568066</v>
+        <v>5.007193928048107</v>
       </c>
       <c r="D3" t="n">
-        <v>31.29854535785624</v>
+        <v>5.086013620651639</v>
       </c>
       <c r="E3" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F3" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.34864305608762</v>
+        <v>5.419154496614238</v>
       </c>
       <c r="D4" t="n">
-        <v>34.11470608100473</v>
+        <v>5.543639738163268</v>
       </c>
       <c r="E4" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F4" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.17076414969474</v>
+        <v>2.790249174325395</v>
       </c>
       <c r="D5" t="n">
-        <v>17.58535820609326</v>
+        <v>2.857620708490155</v>
       </c>
       <c r="E5" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F5" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.7401777208766</v>
+        <v>2.882778879642447</v>
       </c>
       <c r="D6" t="n">
-        <v>18.70816900842964</v>
+        <v>3.040077463869817</v>
       </c>
       <c r="E6" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F6" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.05993233330843</v>
+        <v>2.772239004162619</v>
       </c>
       <c r="D7" t="n">
-        <v>16.67596579996767</v>
+        <v>2.709844442494747</v>
       </c>
       <c r="E7" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F7" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.66199057587868</v>
+        <v>5.632573468580286</v>
       </c>
       <c r="D8" t="n">
-        <v>33.67155861571975</v>
+        <v>5.47162827505446</v>
       </c>
       <c r="E8" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F8" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.09568242381194</v>
+        <v>4.40304839386944</v>
       </c>
       <c r="D9" t="n">
-        <v>26.15357977328386</v>
+        <v>4.249956713158626</v>
       </c>
       <c r="E9" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F9" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.26399108388631</v>
+        <v>4.430398551131525</v>
       </c>
       <c r="D10" t="n">
-        <v>30.98236412808438</v>
+        <v>5.034634170813713</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F10" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.20781033963039</v>
+        <v>5.721269180189939</v>
       </c>
       <c r="D11" t="n">
-        <v>34.13146078893865</v>
+        <v>5.54636237820253</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F11" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>4.390227981884779</v>
+        <v>0.7134120470562766</v>
       </c>
       <c r="D12" t="n">
-        <v>2.747572449342848</v>
+        <v>0.4464805230182128</v>
       </c>
       <c r="E12" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F12" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.20043926638405</v>
+        <v>4.257571380787408</v>
       </c>
       <c r="D13" t="n">
-        <v>33.83873530552769</v>
+        <v>5.49879448714825</v>
       </c>
       <c r="E13" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F13" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6.464513966912155</v>
+        <v>1.050483519623225</v>
       </c>
       <c r="D14" t="n">
-        <v>9.51535855452833</v>
+        <v>1.546245765110854</v>
       </c>
       <c r="E14" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F14" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>29.43051690751943</v>
+        <v>4.782458997471908</v>
       </c>
       <c r="D15" t="n">
-        <v>34.75679369757988</v>
+        <v>5.647978975856731</v>
       </c>
       <c r="E15" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F15" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.563629946389568</v>
+        <v>1.554089866288305</v>
       </c>
       <c r="D16" t="n">
-        <v>19.72386852032981</v>
+        <v>3.205128634553594</v>
       </c>
       <c r="E16" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F16" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>6.62533897373647</v>
+        <v>1.076617583232176</v>
       </c>
       <c r="D17" t="n">
-        <v>16.39830238127271</v>
+        <v>2.664724136956816</v>
       </c>
       <c r="E17" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F17" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.48630480679513</v>
+        <v>5.279024531104208</v>
       </c>
       <c r="D18" t="n">
-        <v>32.49341050723525</v>
+        <v>5.280179207425729</v>
       </c>
       <c r="E18" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F18" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>18.11202811458403</v>
+        <v>2.943204568619905</v>
       </c>
       <c r="D19" t="n">
-        <v>4.464562904918739</v>
+        <v>0.7254914720492951</v>
       </c>
       <c r="E19" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F19" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>28.9216656717018</v>
+        <v>4.699770671651542</v>
       </c>
       <c r="D20" t="n">
-        <v>6.680626912450722</v>
+        <v>1.085601873273242</v>
       </c>
       <c r="E20" t="n">
-        <v>10.22430925091077</v>
+        <v>1.661450253273001</v>
       </c>
       <c r="F20" t="n">
-        <v>11.06789405504428</v>
+        <v>1.798532783944697</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
